--- a/data/sampling/metadata.xlsx
+++ b/data/sampling/metadata.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Liam/Desktop/UW/ECM/alhic1901_deep_layering/github/data/sampling/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Liam/Desktop/UW/paper2/github/data/sampling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{354E1BC5-BF7C-2349-BFAE-2A63B29CDCD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45152098-A3A5-E143-A889-8AB2F9E91F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1020" yWindow="760" windowWidth="29220" windowHeight="18880" xr2:uid="{A8C00553-77EA-744E-A26E-6C00C0051891}"/>
   </bookViews>
@@ -609,7 +609,7 @@
         <v>30</v>
       </c>
       <c r="J3" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -849,7 +849,7 @@
         <v>35</v>
       </c>
       <c r="J12" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">

--- a/data/sampling/metadata.xlsx
+++ b/data/sampling/metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Liam/Desktop/UW/paper2/github/data/sampling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45152098-A3A5-E143-A889-8AB2F9E91F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7504C21-2A77-F045-A079-1BC39DC2282B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1020" yWindow="760" windowWidth="29220" windowHeight="18880" xr2:uid="{A8C00553-77EA-744E-A26E-6C00C0051891}"/>
+    <workbookView xWindow="-20660" yWindow="-22000" windowWidth="29160" windowHeight="18880" xr2:uid="{A8C00553-77EA-744E-A26E-6C00C0051891}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/data/sampling/metadata.xlsx
+++ b/data/sampling/metadata.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Liam/Desktop/UW/paper2/github/data/sampling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7504C21-2A77-F045-A079-1BC39DC2282B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51FEC93C-3DA8-C04F-AD6B-8D5B5B0B06BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20660" yWindow="-22000" windowWidth="29160" windowHeight="18880" xr2:uid="{A8C00553-77EA-744E-A26E-6C00C0051891}"/>
+    <workbookView xWindow="6140" yWindow="760" windowWidth="24000" windowHeight="18880" xr2:uid="{A8C00553-77EA-744E-A26E-6C00C0051891}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="not_in_use" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="40">
   <si>
     <t>section</t>
   </si>
@@ -144,6 +145,18 @@
   </si>
   <si>
     <t>lco2</t>
+  </si>
+  <si>
+    <t>$\delta^{13}$C</t>
+  </si>
+  <si>
+    <t>d13C</t>
+  </si>
+  <si>
+    <t>o2n2</t>
+  </si>
+  <si>
+    <t>Gas</t>
   </si>
 </sst>
 </file>
@@ -522,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCD79FB1-660A-A74C-AF5D-70A1289F30BA}">
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="10" max="10" width="10.83203125" style="1"/>
@@ -1032,6 +1045,68 @@
         <v>7</v>
       </c>
     </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="1">
+        <v>25</v>
+      </c>
+      <c r="E19" s="1">
+        <v>50</v>
+      </c>
+      <c r="F19" s="1">
+        <v>30</v>
+      </c>
+      <c r="G19" s="1">
+        <v>60</v>
+      </c>
+      <c r="J19" s="1">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D824AE80-B0E5-B841-BC03-4FE4D0E27D40}">
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="1">
+        <v>0</v>
+      </c>
+      <c r="E1" s="1">
+        <v>25</v>
+      </c>
+      <c r="F1" s="1">
+        <v>30</v>
+      </c>
+      <c r="G1" s="1">
+        <v>60</v>
+      </c>
+      <c r="J1" s="1">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
